--- a/17 18 20/2 Tableau/6.Data Modeling/4.Data Blending/Data/Sales.xlsx
+++ b/17 18 20/2 Tableau/6.Data Modeling/4.Data Blending/Data/Sales.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\2 Tableau\4.Working with Data Uniion Joins Relationhsip, Data Blending\3) Data Blending\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\2 Tableau\6.Data Modeling\4.Data Blending\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -372,24 +372,27 @@
     <t>Avery Rogers</t>
   </si>
   <si>
-    <t>Product Unique Number</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
-    <t>Sub-Category</t>
-  </si>
-  <si>
     <t>Office Supplies</t>
   </si>
   <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Sub-Cat ID</t>
+  </si>
+  <si>
+    <t>Sub-Cat</t>
+  </si>
+  <si>
     <t>Labels</t>
   </si>
   <si>
-    <t>Furniture</t>
-  </si>
-  <si>
     <t>Furnishings</t>
   </si>
   <si>
@@ -403,9 +406,6 @@
   </si>
   <si>
     <t>Envelopes</t>
-  </si>
-  <si>
-    <t>Technology</t>
   </si>
   <si>
     <t>Phones</t>
@@ -1292,13 +1292,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>7</v>
@@ -1333,10 +1333,10 @@
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>15</v>
@@ -1374,10 +1374,10 @@
         <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>21</v>
@@ -1415,10 +1415,10 @@
         <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>27</v>
@@ -1456,10 +1456,10 @@
         <v>31</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>32</v>
@@ -1497,10 +1497,10 @@
         <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>36</v>
@@ -1538,10 +1538,10 @@
         <v>39</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>40</v>
@@ -1579,7 +1579,7 @@
         <v>43</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>129</v>
@@ -1620,7 +1620,7 @@
         <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>130</v>
@@ -1661,7 +1661,7 @@
         <v>20</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>131</v>
@@ -1702,7 +1702,7 @@
         <v>54</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>132</v>
@@ -1743,7 +1743,7 @@
         <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>133</v>
@@ -1784,7 +1784,7 @@
         <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>134</v>
@@ -1825,7 +1825,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>135</v>
@@ -1866,7 +1866,7 @@
         <v>69</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>136</v>
@@ -1907,10 +1907,10 @@
         <v>73</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>21</v>
@@ -1948,10 +1948,10 @@
         <v>76</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>15</v>
@@ -1989,7 +1989,7 @@
         <v>79</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>129</v>
@@ -2030,10 +2030,10 @@
         <v>82</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>40</v>
@@ -2071,7 +2071,7 @@
         <v>85</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>130</v>
@@ -2112,7 +2112,7 @@
         <v>88</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>132</v>
@@ -2153,10 +2153,10 @@
         <v>14</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>32</v>
@@ -2194,10 +2194,10 @@
         <v>93</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>36</v>
@@ -2235,10 +2235,10 @@
         <v>96</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>27</v>
@@ -2276,7 +2276,7 @@
         <v>99</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>131</v>
@@ -2317,7 +2317,7 @@
         <v>102</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>135</v>
@@ -2358,7 +2358,7 @@
         <v>105</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>134</v>
@@ -2399,7 +2399,7 @@
         <v>108</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>133</v>
@@ -2440,7 +2440,7 @@
         <v>111</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>136</v>
@@ -2481,7 +2481,7 @@
         <v>114</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>129</v>
@@ -2522,10 +2522,10 @@
         <v>31</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>15</v>
